--- a/data/trans_dic/P3A$otraSIcobra-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P3A$otraSIcobra-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que al menos, otra persona que no reside en el hogar y cobra por ello, se ocupa principalmente de las tareas domésticas</t>
+          <t>Hogares en los que, al menos, principalmente otra persona que no reside en el hogar y cobra por ello se ocupa de las tareas domésticas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,26; 4,68</t>
+          <t>1,2; 4,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,03; 3,84</t>
+          <t>1,11; 3,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,5; 3,56</t>
+          <t>1,39; 3,49</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,24; 4,4</t>
+          <t>1,16; 4,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,97; 4,43</t>
+          <t>2,02; 4,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,92; 3,78</t>
+          <t>1,87; 3,91</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,82; 6,96</t>
+          <t>2,59; 6,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,85; 7,9</t>
+          <t>3,83; 7,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,76; 6,55</t>
+          <t>3,81; 6,62</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,94; 8,47</t>
+          <t>2,94; 8,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,95; 5,16</t>
+          <t>2,03; 5,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,71; 5,75</t>
+          <t>2,84; 5,84</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,28; 3,1</t>
+          <t>0,37; 3,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,96</t>
+          <t>0,34; 2,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,03</t>
+          <t>0,57; 2,01</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,85; 4,83</t>
+          <t>1,96; 5,02</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,35; 7,85</t>
+          <t>3,12; 7,33</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,89; 5,5</t>
+          <t>2,83; 5,49</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,3; 6,25</t>
+          <t>2,36; 6,5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,79; 5,55</t>
+          <t>1,71; 5,69</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,27; 5,19</t>
+          <t>2,44; 5,26</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,97</t>
+          <t>0,43; 2,09</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,66; 3,46</t>
+          <t>1,66; 3,42</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,37</t>
+          <t>1,05; 2,41</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,06; 3,43</t>
+          <t>2,11; 3,41</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,73; 3,84</t>
+          <t>2,68; 3,88</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,61; 3,5</t>
+          <t>2,6; 3,53</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que al menos, otra persona que no reside en el hogar y cobra por ello, se ocupa principalmente de las tareas domésticas</t>
+          <t>Hogares en los que, al menos, principalmente otra persona que no reside en el hogar y cobra por ello se ocupa de las tareas domésticas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3915; 14584</t>
+          <t>3724; 13679</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2987; 11115</t>
+          <t>3214; 11014</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9027; 21401</t>
+          <t>8385; 21002</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6404; 22831</t>
+          <t>5991; 23601</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10136; 22818</t>
+          <t>10408; 22041</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19822; 39101</t>
+          <t>19300; 40451</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8893; 21954</t>
+          <t>8180; 20832</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>13379; 27481</t>
+          <t>13315; 27512</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24948; 43427</t>
+          <t>25251; 43896</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9174; 26474</t>
+          <t>9201; 25966</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9283; 24568</t>
+          <t>9671; 26020</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>21338; 45317</t>
+          <t>22351; 46064</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>498; 5527</t>
+          <t>652; 6125</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>838; 5061</t>
+          <t>885; 5545</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2381; 8868</t>
+          <t>2485; 8766</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4978; 13033</t>
+          <t>5295; 13525</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8605; 20175</t>
+          <t>8015; 18837</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15242; 28986</t>
+          <t>14918; 28906</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>14373; 39017</t>
+          <t>14707; 40565</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>15205; 47118</t>
+          <t>14523; 48346</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>33382; 76513</t>
+          <t>35946; 77566</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>4013; 18305</t>
+          <t>3967; 19403</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>11930; 24824</t>
+          <t>11930; 24535</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>16454; 39098</t>
+          <t>17270; 39747</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>71217; 118540</t>
+          <t>72969; 117979</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>101413; 142650</t>
+          <t>99331; 143985</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>187029; 251003</t>
+          <t>186252; 253087</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P3A$otraSIcobra-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P3A$otraSIcobra-Provincia-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,2; 4,39</t>
+          <t>1,19; 4,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,11; 3,8</t>
+          <t>1,0; 3,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,39; 3,49</t>
+          <t>1,33; 3,25</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,16; 4,55</t>
+          <t>1,28; 4,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,02; 4,28</t>
+          <t>1,92; 4,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,87; 3,91</t>
+          <t>1,96; 3,92</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,59; 6,6</t>
+          <t>2,78; 6,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,83; 7,91</t>
+          <t>3,89; 7,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,81; 6,62</t>
+          <t>3,81; 6,43</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,94; 8,31</t>
+          <t>3,13; 8,46</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,03; 5,47</t>
+          <t>3,1; 6,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,84; 5,84</t>
+          <t>3,41; 6,37</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,44</t>
+          <t>0,36; 3,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,14</t>
+          <t>0,49; 2,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,01</t>
+          <t>0,62; 2,08</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,96; 5,02</t>
+          <t>1,91; 4,7</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,12; 7,33</t>
+          <t>2,96; 7,64</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,83; 5,49</t>
+          <t>2,94; 5,47</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,36; 6,5</t>
+          <t>2,65; 5,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,71; 5,69</t>
+          <t>4,06; 6,72</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,44; 5,26</t>
+          <t>3,63; 5,94</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,09</t>
+          <t>0,81; 2,41</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,66; 3,42</t>
+          <t>1,71; 3,56</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,05; 2,41</t>
+          <t>1,43; 2,66</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,11; 3,41</t>
+          <t>2,43; 3,62</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,68; 3,88</t>
+          <t>3,16; 4,18</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,6; 3,53</t>
+          <t>2,96; 3,69</t>
         </is>
       </c>
     </row>
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7988</t>
+          <t>7569</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5986</t>
+          <t>6209</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13974</t>
+          <t>13777</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3724; 13679</t>
+          <t>3781; 14244</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3214; 11014</t>
+          <t>3163; 10667</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8385; 21002</t>
+          <t>8426; 20663</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>12235</t>
+          <t>12829</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>15471</t>
+          <t>16459</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>27706</t>
+          <t>29288</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5991; 23601</t>
+          <t>6819; 24772</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10408; 22041</t>
+          <t>10517; 23049</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19300; 40451</t>
+          <t>21148; 42276</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14095</t>
+          <t>13711</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>19111</t>
+          <t>19442</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33206</t>
+          <t>33153</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8180; 20832</t>
+          <t>8768; 20916</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>13315; 27512</t>
+          <t>13798; 27566</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>25251; 43896</t>
+          <t>25535; 43141</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>15262</t>
+          <t>18685</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>17152</t>
+          <t>18442</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>32414</t>
+          <t>37127</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9201; 25966</t>
+          <t>11676; 31560</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9671; 26020</t>
+          <t>13089; 25907</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22351; 46064</t>
+          <t>27080; 50613</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2569</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2551</t>
+          <t>2685</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4878</t>
+          <t>5254</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>652; 6125</t>
+          <t>738; 6307</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>885; 5545</t>
+          <t>1132; 5472</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2485; 8766</t>
+          <t>2695; 9015</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>8498</t>
+          <t>8437</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>12730</t>
+          <t>12769</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>21228</t>
+          <t>21206</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5295; 13525</t>
+          <t>5160; 12721</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8015; 18837</t>
+          <t>7795; 20150</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>14918; 28906</t>
+          <t>15734; 29223</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>24090</t>
+          <t>28362</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>33234</t>
+          <t>41491</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>57324</t>
+          <t>69853</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>14707; 40565</t>
+          <t>19042; 43002</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>14523; 48346</t>
+          <t>31308; 51864</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>35946; 77566</t>
+          <t>54121; 88603</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>10717</t>
+          <t>11766</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>17649</t>
+          <t>20375</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>28367</t>
+          <t>32141</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>3967; 19403</t>
+          <t>6473; 19262</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>11930; 24535</t>
+          <t>14205; 29579</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>17270; 39747</t>
+          <t>23332; 43286</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>95211</t>
+          <t>103927</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>123885</t>
+          <t>137872</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>219096</t>
+          <t>241799</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>72969; 117979</t>
+          <t>85939; 127884</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>99331; 143985</t>
+          <t>118070; 156332</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>186252; 253087</t>
+          <t>215168; 268184</t>
         </is>
       </c>
     </row>
